--- a/artfynd/A 22604-2024 artfynd.xlsx
+++ b/artfynd/A 22604-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>57040208</v>
       </c>
       <c r="B2" t="n">
-        <v>95591</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525858.0511541432</v>
+        <v>525858</v>
       </c>
       <c r="R2" t="n">
-        <v>6578083.775140243</v>
+        <v>6578084</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -752,19 +747,9 @@
           <t>1980-07-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1980-07-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
